--- a/artfynd/A 44095-2023 artfynd.xlsx
+++ b/artfynd/A 44095-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44095-2023 artfynd.xlsx
+++ b/artfynd/A 44095-2023 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16878816</v>
+        <v>67135998</v>
       </c>
       <c r="B2" t="n">
-        <v>57435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -709,19 +704,30 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rågåsmyren, Vrm</t>
+          <t>Kvarnmyren, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413787.8065542982</v>
+        <v>413788</v>
       </c>
       <c r="R2" t="n">
-        <v>6685803.777298434</v>
+        <v>6685804</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,26 +751,21 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-09-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-02-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-09-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-02-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färsk spillning, kana och spår ca en dag gamla.</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -779,23 +780,23 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Bro över stenigt och blockigt mindre vattendrag. Blandskog i omgivningen.</t>
+          <t>Istäckt vattendrag med stort hålrum mellan vattenyta och is.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Therese Ericsson</t>
+          <t>Dan Mangsbo</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Therese Ericsson</t>
+          <t>klara linder, Jessica Lerstorp, Elias Elmström, Maja Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Övervakning av utter i Värmlands län - barmarksinventering</t>
+          <t>Övervakning av utter i Värmlands län - vinterspårning</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 44095-2023 artfynd.xlsx
+++ b/artfynd/A 44095-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,8 +804,16 @@
           <t>Övervakning av utter i Värmlands län - vinterspårning</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67135998</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>